--- a/data/raw/sales/Week 21/White_Mulberry/other_channels.xlsx
+++ b/data/raw/sales/Week 21/White_Mulberry/other_channels.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 21\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26A481C-7DCF-4325-A6C3-452B10D36B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA705FC0-D099-4299-A513-A883DD402F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B2B" sheetId="12" r:id="rId1"/>
-    <sheet name="1P" sheetId="13" r:id="rId2"/>
+    <sheet name="1p Sales" sheetId="13" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
